--- a/parameters/UA/hydrogen/country_parameters.xlsx
+++ b/parameters/UA/hydrogen/country_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/engs2859_ox_ac_uk/Documents/Geo-X/Geo-X/parameters/UA/hydrogen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54DBAA6-B1AF-47BA-B642-1B4C95D47D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1F4AD5CC-4147-E441-ACC6-A362C24513B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25029A7D-1E65-534F-BC7A-F795A35BDAE1}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{60BD1E41-9A81-F547-A629-52DD9269BE2D}"/>
+    <workbookView xWindow="3880" yWindow="3880" windowWidth="21600" windowHeight="11300" xr2:uid="{60BD1E41-9A81-F547-A629-52DD9269BE2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,6 +135,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,26 +439,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A655327-FB0F-D040-A870-A9F18A82B881}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
